--- a/pacjenci/DOROTA WRÓBEL.xlsx
+++ b/pacjenci/DOROTA WRÓBEL.xlsx
@@ -485,7 +485,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -529,7 +529,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -573,7 +573,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -617,7 +617,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/pacjenci/DOROTA WRÓBEL.xlsx
+++ b/pacjenci/DOROTA WRÓBEL.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>22.11.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy guzkowaty (grudkowy) FL G3A. Ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 99 mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie, pojedyncze i spakietowane węzły chłonne: - podostrogowe wielkości 50x32x66 mm wg PET SUV max 21,2; - we wnęce płuca prawego wielkości 22x17x31 mm wg PET SUV max 19,4; - przytchawicze dolne prawe wielkości do 11 mm SUV max 6,6; - przytchawicze dolne lewe wielkości do 19x9 mm SUV max 8,8.  Aktywny metabolicznie naciek miękkotkankowy w topografii węzłów chłonnych okołoaortalnych lewych i przykręgosłupowych lewych od poziomu Th8/Th9 do Th11 - o największych wymiarach 28 mm [Im fuz. 136] x55 mm [Im fuz. 139] wg PET na długości 54 mm wg PET SUV max do 13,1.  Aktywne i pobudzone metabolicznie węzły chłonne przykręgosłupowo po stronie prawej na poziomie Th10/Th11-Th12, wielkości do 12x9mm wg PET  SUV max do 5,2.   Wzmożony metabolizm FDG w zmianach naciekowo-włóknistych w segmencie 4 oraz nieco 5 i 8 płuca lewego, na obszarze wielkości ok. 33x14mm, SUV max 5,2- zmiany zapalne? inne? Obszar pobudzenia metabolicznego w topografii segmentu 6 płuca prawego, średnicy 7mm wg PET SUV max 3,9 - bez jednoznacznych zmian widocznych w przeglądowym badaniu TK - zlep płytkowy? [Im fuz.111]  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 5,2- w pierwszej kolejności o charakterze czynnościowym Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe i udowe obustronnie, wielkości do 11x9mm, SUV max do 1,8.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo w odcinku piersiowym kręgosłupa nierówne obrysy i sklerotyzacji [typu Modic 3] blaszek granicznych trzonów kręgowych. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Miernie sklerotyczna przebudowa trzonu S1. Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w topografii skóry i tkanki podskórnej oraz w mięśniach przykręgosłupowo po stronie lewej (SUV max do 5,9) w topografii m-ca po biopsji otwartej - procesy gojenia. Żylaki w przednio-górnej części uda lewego.  Wartości referencyjne: MBPS SUVmax 2,3; Prawy płat wątroby SUVmax do 3,8.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F/FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej z zajęciem węzłów chłonnych nadprzeponowo. Wzmożony metabolizm FDG w zmianach naciekowo-włóknistych w płucu lewym - zmiany zapalne? inne? Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>21.2</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>04.04.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy guzkowaty (grudkowy) FL G3A. Ocena remisji po 3 cyklach chemioterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 62 min od podania 18F-FDG. Glikemia: 94mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne: we wnęce płuca prawego wielkości 20 mm, SUV max 3,1. Miernie pobudzony metabolicznie obszar zmian włóknistych oraz o typie mlecznej szyby w segmencie 6/10 płuca prawego, przykręgosłupowo, wielkości ok. 35x16mm wg PET,  SUV max 3,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego.  Drobne zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo zwiększony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe i udowe obustronnie, wielkości do 11x9mm, SUV max do 1,8.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym objętym badaniem - związane ze stosowanym leczeniem?- do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo w odcinku piersiowym kręgosłupa nierówne obrysy i sklerotyzacja [typu Modic 3] blaszek granicznych trzonów kręgowych. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Miernie sklerotyczna przebudowa trzonu S1. Os sacrum arcuatum.  Inne: Żylaki w przednio-górnej części uda lewego.  Wartości referencyjne: MBPS SUVmax 2,7; Prawy płat wątroby SUVmax do 4,6.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F/FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>4.6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>09.08.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy guzkowaty (grudkowy) FL G3A. Ocena remisji choroby po zakończeniu immunochemioterapii..</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 87mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego.  Zmiany włókniste oraz niewielkie obszary o typie mlecznej szyby w segmencie 6/10 płuca prawego, przykręgosłupowo. Niewielkie zmiany włókniste w segm. 4 i 5 płuca lewego. Drobne zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo zwiększony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe i udowe obustronnie, wielkości do 16x14mm, SUV max do 1,9.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym objętym badaniem - związane ze stosowanym leczeniem? - do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo w odcinku piersiowym kręgosłupa nierówne obrysy i sklerotyzacja [typu Modic 3] blaszek granicznych trzonów kręgowych. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Miernie sklerotyczna przebudowa trzonu S1. Os sacrum arcuatum.  Inne: Żylaki w przednio-górnej części uda lewego.  Wartości referencyjne: MBPS SUVmax 2,7; Prawy płat wątroby SUVmax do 3,5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F/FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3.5</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>16.03.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy guzkowaty (grudkowy) FL G3A. Ocena remisji choroby po zakończeniu immunochemioterapii.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 68mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego.  Zmiany włókniste oraz niewielkie obszary o typie mlecznej szyby w segmencie 6/10 płuca prawego, przykręgosłupowo. Niewielkie zmiany włókniste w segm. 4 i 5 płuca lewego. Drobne zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo zwiększony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe i udowe obustronnie, wielkości do 16x14mm, SUV max do 1,9.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym objętym badaniem - związane ze stosowanym leczeniem? - do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo w odcinku piersiowym kręgosłupa nierówne obrysy i sklerotyzacja [typu Modic 3] blaszek granicznych trzonów kręgowych. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Miernie sklerotyczna przebudowa trzonu S1. Os sacrum arcuatum.  Inne: Żylaki w przednio-górnej części uda lewego.  Wartości referencyjne: MBPS SUVmax 3,2; Prawy płat wątroby SUVmax do 4,4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F/FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej. W porównaniu do badania PET/CT z 09.08.2022 obraz PET/CT z 18F-FDG bez istotnych różnic</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>4.4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/DOROTA WRÓBEL.xlsx
+++ b/pacjenci/DOROTA WRÓBEL.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 99 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie, pojedyncze i spakietowane węzły chłonne: - podostrogowe wielkości 50x32x66 mm wg PET SUV max 21,2; - we wnęce płuca prawego wielkości 22x17x31 mm wg PET SUV max 19,4; - przytchawicze dolne prawe wielkości do 11 mm SUV max 6,6; - przytchawicze dolne lewe wielkości do 19x9 mm SUV max 8,8.  Aktywny metabolicznie naciek miękkotkankowy w topografii węzłów chłonnych okołoaortalnych lewych i przykręgosłupowych lewych od poziomu Th8/Th9 do Th11 - o największych wymiarach 28 mm [Im fuz. 136] x55 mm [Im fuz. 139] wg PET na długości 54 mm wg PET SUV max do 13,1.  Aktywne i pobudzone metabolicznie węzły chłonne przykręgosłupowo po stronie prawej na poziomie Th10/Th11-Th12, wielkości do 12x9mm wg PET  SUV max do 5,2.   Wzmożony metabolizm FDG w zmianach naciekowo-włóknistych w segmencie 4 oraz nieco 5 i 8 płuca lewego, na obszarze wielkości ok. 33x14mm, SUV max 5,2- zmiany zapalne? inne? Obszar pobudzenia metabolicznego w topografii segmentu 6 płuca prawego, średnicy 7mm wg PET SUV max 3,9 - bez jednoznacznych zmian widocznych w przeglądowym badaniu TK - zlep płytkowy? [Im fuz.111]  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 5,2- w pierwszej kolejności o charakterze czynnościowym Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe i udowe obustronnie, wielkości do 11x9mm, SUV max do 1,8.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo w odcinku piersiowym kręgosłupa nierówne obrysy i sklerotyzacji [typu Modic 3] blaszek granicznych trzonów kręgowych. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Miernie sklerotyczna przebudowa trzonu S1. Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w topografii skóry i tkanki podskórnej oraz w mięśniach przykręgosłupowo po stronie lewej (SUV max do 5,9) w topografii m-ca po biopsji otwartej - procesy gojenia. Żylaki w przednio-górnej części uda lewego.  Wartości referencyjne: MBPS SUVmax 2,3; Prawy płat wątroby SUVmax do 3,8.</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie, pojedyncze i spakietowane węzły chłonne: - podostrogowe wielkości 50x32x66 mm wg PET SUV max 21,2; - we wnęce płuca prawego wielkości 22x17x31 mm wg PET SUV max 19,4; - przytchawicze dolne prawe wielkości do 11 mm SUV max 6,6; - przytchawicze dolne lewe wielkości do 19x9 mm SUV max 8,8.  Aktywny metabolicznie naciek miękkotkankowy w topografii węzłów chłonnych okołoaortalnych lewych i przykręgosłupowych lewych od poziomu Th8/Th9 do Th11 - o największych wymiarach 28 mm [Im fuz. 136] x55 mm [Im fuz. 139] wg PET na długości 54 mm wg PET SUV max do 13,1.  Aktywne i pobudzone metabolicznie węzły chłonne przykręgosłupowo po stronie prawej na poziomie Th10/Th11-Th12, wielkości do 12x9mm wg PET  SUV max do 5,2.   Wzmożony metabolizm FDG w zmianach naciekowo-włóknistych w segmencie 4 oraz nieco 5 i 8 płuca lewego, na obszarze wielkości ok. 33x14mm, SUV max 5,2- zmiany zapalne? inne? Obszar pobudzenia metabolicznego w topografii segmentu 6 płuca prawego, średnicy 7mm wg PET SUV max 3,9 - bez jednoznacznych zmian widocznych w przeglądowym badaniu TK - zlep płytkowy? [Im fuz.111]  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 5,2- w pierwszej kolejności o charakterze czynnościowym Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe i udowe obustronnie, wielkości do 11x9mm, SUV max do 1,8.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo w odcinku piersiowym kręgosłupa nierówne obrysy i sklerotyzacji [typu Modic 3] blaszek granicznych trzonów kręgowych. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Miernie sklerotyczna przebudowa trzonu S1. Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w topografii skóry i tkanki podskórnej oraz w mięśniach przykręgosłupowo po stronie lewej (SUV max do 5,9) w topografii m-ca po biopsji otwartej - procesy gojenia. Żylaki w przednio-górnej części uda lewego.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F/FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej z zajęciem węzłów chłonnych nadprzeponowo. Wzmożony metabolizm FDG w zmianach naciekowo-włóknistych w płucu lewym - zmiany zapalne? inne? Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>21.2</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 62 min od podania 18F-FDG. Glikemia: 94mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne: we wnęce płuca prawego wielkości 20 mm, SUV max 3,1. Miernie pobudzony metabolicznie obszar zmian włóknistych oraz o typie mlecznej szyby w segmencie 6/10 płuca prawego, przykręgosłupowo, wielkości ok. 35x16mm wg PET,  SUV max 3,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego.  Drobne zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo zwiększony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe i udowe obustronnie, wielkości do 11x9mm, SUV max do 1,8.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym objętym badaniem - związane ze stosowanym leczeniem?- do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo w odcinku piersiowym kręgosłupa nierówne obrysy i sklerotyzacja [typu Modic 3] blaszek granicznych trzonów kręgowych. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Miernie sklerotyczna przebudowa trzonu S1. Os sacrum arcuatum.  Inne: Żylaki w przednio-górnej części uda lewego.  Wartości referencyjne: MBPS SUVmax 2,7; Prawy płat wątroby SUVmax do 4,6.</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie węzły chłonne: we wnęce płuca prawego wielkości 20 mm, SUV max 3,1. Miernie pobudzony metabolicznie obszar zmian włóknistych oraz o typie mlecznej szyby w segmencie 6/10 płuca prawego, przykręgosłupowo, wielkości ok. 35x16mm wg PET,  SUV max 3,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego.  Drobne zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Odcinkowo zwiększony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe i udowe obustronnie, wielkości do 11x9mm, SUV max do 1,8.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w układzie kostnym objętym badaniem - związane ze stosowanym leczeniem?- do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo w odcinku piersiowym kręgosłupa nierówne obrysy i sklerotyzacja [typu Modic 3] blaszek granicznych trzonów kręgowych. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Miernie sklerotyczna przebudowa trzonu S1. Os sacrum arcuatum.  Inne: Żylaki w przednio-górnej części uda lewego.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F/FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>4.6</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 87mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego.  Zmiany włókniste oraz niewielkie obszary o typie mlecznej szyby w segmencie 6/10 płuca prawego, przykręgosłupowo. Niewielkie zmiany włókniste w segm. 4 i 5 płuca lewego. Drobne zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo zwiększony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe i udowe obustronnie, wielkości do 16x14mm, SUV max do 1,9.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym objętym badaniem - związane ze stosowanym leczeniem? - do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo w odcinku piersiowym kręgosłupa nierówne obrysy i sklerotyzacja [typu Modic 3] blaszek granicznych trzonów kręgowych. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Miernie sklerotyczna przebudowa trzonu S1. Os sacrum arcuatum.  Inne: Żylaki w przednio-górnej części uda lewego.  Wartości referencyjne: MBPS SUVmax 2,7; Prawy płat wątroby SUVmax do 3,5</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego.  Zmiany włókniste oraz niewielkie obszary o typie mlecznej szyby w segmencie 6/10 płuca prawego, przykręgosłupowo. Niewielkie zmiany włókniste w segm. 4 i 5 płuca lewego. Drobne zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Odcinkowo zwiększony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe i udowe obustronnie, wielkości do 16x14mm, SUV max do 1,9.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w układzie kostnym objętym badaniem - związane ze stosowanym leczeniem? - do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo w odcinku piersiowym kręgosłupa nierówne obrysy i sklerotyzacja [typu Modic 3] blaszek granicznych trzonów kręgowych. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Miernie sklerotyczna przebudowa trzonu S1. Os sacrum arcuatum.  Inne: Żylaki w przednio-górnej części uda lewego.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F/FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 68mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego.  Zmiany włókniste oraz niewielkie obszary o typie mlecznej szyby w segmencie 6/10 płuca prawego, przykręgosłupowo. Niewielkie zmiany włókniste w segm. 4 i 5 płuca lewego. Drobne zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo zwiększony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe i udowe obustronnie, wielkości do 16x14mm, SUV max do 1,9.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym objętym badaniem - związane ze stosowanym leczeniem? - do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo w odcinku piersiowym kręgosłupa nierówne obrysy i sklerotyzacja [typu Modic 3] blaszek granicznych trzonów kręgowych. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Miernie sklerotyczna przebudowa trzonu S1. Os sacrum arcuatum.  Inne: Żylaki w przednio-górnej części uda lewego.  Wartości referencyjne: MBPS SUVmax 3,2; Prawy płat wątroby SUVmax do 4,4</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego.  Zmiany włókniste oraz niewielkie obszary o typie mlecznej szyby w segmencie 6/10 płuca prawego, przykręgosłupowo. Niewielkie zmiany włókniste w segm. 4 i 5 płuca lewego. Drobne zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Odcinkowo zwiększony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe i udowe obustronnie, wielkości do 16x14mm, SUV max do 1,9.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w układzie kostnym objętym badaniem - związane ze stosowanym leczeniem? - do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo w odcinku piersiowym kręgosłupa nierówne obrysy i sklerotyzacja [typu Modic 3] blaszek granicznych trzonów kręgowych. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Miernie sklerotyczna przebudowa trzonu S1. Os sacrum arcuatum.  Inne: Żylaki w przednio-górnej części uda lewego.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F/FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej. W porównaniu do badania PET/CT z 09.08.2022 obraz PET/CT z 18F-FDG bez istotnych różnic</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>4.4</v>
       </c>
     </row>
